--- a/株式会社カナリア/株式会社カナリア_案件マスター_260726.xlsx
+++ b/株式会社カナリア/株式会社カナリア_案件マスター_260726.xlsx
@@ -115,6 +115,34 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">売掛債権は個別に回収可能性を判断するため、貸倒引当金は全額控除（戻入）する。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">新設分割により新設会社へ承継する非事業用資産（面談議事録 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2026/7 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">にて対象に追加）。</t>
         </r>
       </text>
     </comment>
@@ -1604,7 +1632,7 @@
     <t xml:space="preserve">1. 本タブは「修正BS(借方)」「修正BS(貸方) 」の修正後残高（令和8年1月期・評価基準日）を分割前BSとしている。</t>
   </si>
   <si>
-    <t xml:space="preserve">2. 新設分割により、非事業用資産である投資有価証券275,896千円及び保険積立金43,327千円（計319,223千円）を新設会社へ承継する。</t>
+    <t xml:space="preserve">2. 新設分割により、非事業用資産である投資有価証券275,896千円・保険積立金43,327千円・車両運搬具265千円（計319,488千円）を新設会社へ承継する。</t>
   </si>
   <si>
     <t xml:space="preserve">3. 分割型（人的）分割を前提とし、承継純資産と同額だけ分割会社の純資産が減少するものとしている。</t>
@@ -5779,17 +5807,17 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -8530,7 +8558,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="9" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="38" fillId="9" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8538,7 +8566,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="9" borderId="62" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="38" fillId="9" borderId="62" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9890,11 +9918,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="100"/>
-        <c:axId val="90442686"/>
-        <c:axId val="38505493"/>
+        <c:axId val="12114118"/>
+        <c:axId val="44488964"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90442686"/>
+        <c:axId val="12114118"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9927,14 +9955,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38505493"/>
+        <c:crossAx val="44488964"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38505493"/>
+        <c:axId val="44488964"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9974,7 +10002,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90442686"/>
+        <c:crossAx val="12114118"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10297,11 +10325,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="99161025"/>
-        <c:axId val="81852624"/>
+        <c:axId val="54993969"/>
+        <c:axId val="98174136"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99161025"/>
+        <c:axId val="54993969"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10334,7 +10362,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81852624"/>
+        <c:crossAx val="98174136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10342,7 +10370,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81852624"/>
+        <c:axId val="98174136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10372,7 +10400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99161025"/>
+        <c:crossAx val="54993969"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10789,11 +10817,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="10011723"/>
-        <c:axId val="9307575"/>
+        <c:axId val="71054952"/>
+        <c:axId val="70066450"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10011723"/>
+        <c:axId val="71054952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10826,7 +10854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9307575"/>
+        <c:crossAx val="70066450"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10834,7 +10862,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9307575"/>
+        <c:axId val="70066450"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10864,7 +10892,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10011723"/>
+        <c:crossAx val="71054952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10936,10 +10964,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.295845027038127"/>
-          <c:y val="0.158108995403808"/>
-          <c:w val="0.440961051406667"/>
-          <c:h val="0.734996717005909"/>
+          <c:x val="0.295796823658269"/>
+          <c:y val="0.15812976096664"/>
+          <c:w val="0.44092278203724"/>
+          <c:h val="0.734961912266877"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -11547,11 +11575,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="63293187"/>
-        <c:axId val="34066004"/>
+        <c:axId val="59677203"/>
+        <c:axId val="57211733"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63293187"/>
+        <c:axId val="59677203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11584,7 +11612,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34066004"/>
+        <c:crossAx val="57211733"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11592,7 +11620,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34066004"/>
+        <c:axId val="57211733"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11622,7 +11650,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63293187"/>
+        <c:crossAx val="59677203"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11827,11 +11855,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="20977748"/>
-        <c:axId val="11055016"/>
+        <c:axId val="86619700"/>
+        <c:axId val="53363940"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20977748"/>
+        <c:axId val="86619700"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11864,7 +11892,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11055016"/>
+        <c:crossAx val="53363940"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11872,7 +11900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11055016"/>
+        <c:axId val="53363940"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11902,7 +11930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20977748"/>
+        <c:crossAx val="86619700"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12072,11 +12100,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="64587299"/>
-        <c:axId val="59304922"/>
+        <c:axId val="81682653"/>
+        <c:axId val="77132659"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64587299"/>
+        <c:axId val="81682653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12109,7 +12137,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59304922"/>
+        <c:crossAx val="77132659"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12117,7 +12145,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59304922"/>
+        <c:axId val="77132659"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12147,7 +12175,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64587299"/>
+        <c:crossAx val="81682653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12183,9 +12211,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>882000</xdr:colOff>
+      <xdr:colOff>881640</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:rowOff>35640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12194,7 +12222,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2655000" y="2503440"/>
-        <a:ext cx="5610240" cy="3209400"/>
+        <a:ext cx="5609880" cy="3209040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12218,9 +12246,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>137520</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>204120</xdr:rowOff>
+      <xdr:rowOff>203760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12229,7 +12257,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4759200" y="206280"/>
-        <a:ext cx="5243040" cy="2741040"/>
+        <a:ext cx="5242680" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12248,9 +12276,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>166320</xdr:colOff>
+      <xdr:colOff>165960</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>172080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12259,7 +12287,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4772160" y="3832200"/>
-        <a:ext cx="5258880" cy="2741040"/>
+        <a:ext cx="5258520" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12278,9 +12306,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>172440</xdr:colOff>
+      <xdr:colOff>172080</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>178920</xdr:rowOff>
+      <xdr:rowOff>178560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12289,7 +12317,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4778280" y="7267680"/>
-        <a:ext cx="5258880" cy="2741040"/>
+        <a:ext cx="5258520" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12308,9 +12336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>311040</xdr:colOff>
+      <xdr:colOff>310680</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>40320</xdr:rowOff>
+      <xdr:rowOff>39960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12319,7 +12347,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4929480" y="10993680"/>
-        <a:ext cx="5246280" cy="2762640"/>
+        <a:ext cx="5245920" cy="2762280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12338,9 +12366,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>137520</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>204120</xdr:rowOff>
+      <xdr:rowOff>203760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12349,7 +12377,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="16141680" y="206280"/>
-        <a:ext cx="5243040" cy="2741040"/>
+        <a:ext cx="5242680" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12368,9 +12396,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>137520</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>204120</xdr:rowOff>
+      <xdr:rowOff>203760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12379,7 +12407,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="16141680" y="4092480"/>
-        <a:ext cx="5243040" cy="2741040"/>
+        <a:ext cx="5242680" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -16073,15 +16101,15 @@
       </c>
       <c r="D20" s="140" t="n">
         <f aca="false">D21+D35+D46</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="E20" s="150" t="n">
         <f aca="false">C20+D20</f>
-        <v>4640036</v>
+        <v>4375168</v>
       </c>
       <c r="F20" s="150" t="n">
         <f aca="false">-D20</f>
-        <v>319223100</v>
+        <v>319487968</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16094,15 +16122,15 @@
       </c>
       <c r="D21" s="34" t="n">
         <f aca="false">SUM(D22:D34)</f>
-        <v>0</v>
+        <v>-264868</v>
       </c>
       <c r="E21" s="151" t="n">
         <f aca="false">C21+D21</f>
-        <v>1056920</v>
+        <v>792052</v>
       </c>
       <c r="F21" s="151" t="n">
         <f aca="false">-D21</f>
-        <v>-0</v>
+        <v>264868</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16131,14 +16159,17 @@
         <f aca="false">'修正BS(借方)'!E23</f>
         <v>264868</v>
       </c>
-      <c r="D23" s="17"/>
+      <c r="D23" s="17" t="n">
+        <f aca="false">-C23</f>
+        <v>-264868</v>
+      </c>
       <c r="E23" s="18" t="n">
         <f aca="false">C23+D23</f>
-        <v>264868</v>
+        <v>0</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">-D23</f>
-        <v>-0</v>
+        <v>264868</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16712,15 +16743,15 @@
       </c>
       <c r="D61" s="172" t="n">
         <f aca="false">D5+D20+D55+D60</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="E61" s="173" t="n">
         <f aca="false">C61+D61</f>
-        <v>230985442</v>
+        <v>230720574</v>
       </c>
       <c r="F61" s="173" t="n">
         <f aca="false">-D61</f>
-        <v>319223100</v>
+        <v>319487968</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17228,15 +17259,15 @@
       </c>
       <c r="D94" s="218" t="n">
         <f aca="false">分割後BS!D61-D82</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="E94" s="150" t="n">
         <f aca="false">C94+D94</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="F94" s="150" t="n">
         <f aca="false">-D94</f>
-        <v>319223100</v>
+        <v>319487968</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17249,15 +17280,15 @@
       </c>
       <c r="D95" s="237" t="n">
         <f aca="false">D85+D88+D89+D92+D93+D94</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="E95" s="238" t="n">
         <f aca="false">C95+D95</f>
-        <v>14513809</v>
+        <v>14248941</v>
       </c>
       <c r="F95" s="238" t="n">
         <f aca="false">-D95</f>
-        <v>319223100</v>
+        <v>319487968</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17270,15 +17301,15 @@
       </c>
       <c r="D96" s="240" t="n">
         <f aca="false">D82+D95</f>
-        <v>-319223100</v>
+        <v>-319487968</v>
       </c>
       <c r="E96" s="241" t="n">
         <f aca="false">C96+D96</f>
-        <v>230985442</v>
+        <v>230720574</v>
       </c>
       <c r="F96" s="241" t="n">
         <f aca="false">-D96</f>
-        <v>319223100</v>
+        <v>319487968</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
